--- a/api/1/clv2/xlsx/fr/SectorGroup.xlsx
+++ b/api/1/clv2/xlsx/fr/SectorGroup.xlsx
@@ -25,18 +25,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,18 +46,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>Education, Niveau non spécifié</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
     <t>111</t>
   </si>
   <si>
-    <t>Education</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>Education, Niveau non spécifié</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -82,12 +82,12 @@
     <t>Enseignement primaire</t>
   </si>
   <si>
+    <t>Education de Base</t>
+  </si>
+  <si>
     <t>112</t>
   </si>
   <si>
-    <t>Education de Base</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>Enseignement secondaire supérieur (modifié et comprend les données de 11322)</t>
   </si>
   <si>
+    <t>Education Secondaire</t>
+  </si>
+  <si>
     <t>113</t>
   </si>
   <si>
-    <t>Education Secondaire</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -148,12 +148,12 @@
     <t>Enseignement supérieur</t>
   </si>
   <si>
+    <t>Education Post Secondaire</t>
+  </si>
+  <si>
     <t>114</t>
   </si>
   <si>
-    <t>Education Post Secondaire</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -166,18 +166,18 @@
     <t>Politique de la santé et gestion administrative</t>
   </si>
   <si>
+    <t>Santé, Général</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>Santé</t>
+  </si>
+  <si>
     <t>121</t>
   </si>
   <si>
-    <t>Santé</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>Santé, Général</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -202,12 +202,12 @@
     <t>Soins et services de santé de base</t>
   </si>
   <si>
+    <t>Santé de Base</t>
+  </si>
+  <si>
     <t>122</t>
   </si>
   <si>
-    <t>Santé de Base</t>
-  </si>
-  <si>
     <t>12230</t>
   </si>
   <si>
@@ -262,12 +262,12 @@
     <t>Lutte contre les MNT, général</t>
   </si>
   <si>
+    <t>Maladies non-transmissibles (MNT)</t>
+  </si>
+  <si>
     <t>123</t>
   </si>
   <si>
-    <t>Maladies non-transmissibles (MNT)</t>
-  </si>
-  <si>
     <t>12320</t>
   </si>
   <si>
@@ -304,12 +304,12 @@
     <t>Politique/programmes en matière de population et gestion administrative</t>
   </si>
   <si>
+    <t>Politique en Matière de Population/Santé&amp;Fertilité</t>
+  </si>
+  <si>
     <t>130</t>
   </si>
   <si>
-    <t>Politique en Matière de Population/Santé&amp;Fertilité</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -340,12 +340,12 @@
     <t>Politique et gestion administrative du secteur de l'eau</t>
   </si>
   <si>
+    <t>Distribution d'Eau et Assainissement</t>
+  </si>
+  <si>
     <t>140</t>
   </si>
   <si>
-    <t>Distribution d'Eau et Assainissement</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -412,18 +412,18 @@
     <t>Politiques publiques et gestion administrative</t>
   </si>
   <si>
+    <t>Gouvernement &amp; Société Civile-général</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>Gouvernement &amp; Société Civile</t>
+  </si>
+  <si>
     <t>151</t>
   </si>
   <si>
-    <t>Gouvernement &amp; Société Civile</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>Gouvernement &amp; Société Civile-général</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -520,12 +520,12 @@
     <t>Gestion et réforme des systèmes de sécurité</t>
   </si>
   <si>
+    <t>Conflits, Paix et Sécurité</t>
+  </si>
+  <si>
     <t>152</t>
   </si>
   <si>
-    <t>Conflits, Paix et Sécurité</t>
-  </si>
-  <si>
     <t>15220</t>
   </si>
   <si>
@@ -562,12 +562,12 @@
     <t>Protection sociale</t>
   </si>
   <si>
+    <t>Infrastructure et Services Sociaux Divers</t>
+  </si>
+  <si>
     <t>160</t>
   </si>
   <si>
-    <t>Infrastructure et Services Sociaux Divers</t>
-  </si>
-  <si>
     <t>16020</t>
   </si>
   <si>
@@ -634,12 +634,12 @@
     <t>Politique des transports et gestion administrative</t>
   </si>
   <si>
+    <t>Transports et Entreposage</t>
+  </si>
+  <si>
     <t>210</t>
   </si>
   <si>
-    <t>Transports et Entreposage</t>
-  </si>
-  <si>
     <t>21020</t>
   </si>
   <si>
@@ -682,12 +682,12 @@
     <t>Politique des communications et gestion administrative</t>
   </si>
   <si>
+    <t>Communications</t>
+  </si>
+  <si>
     <t>220</t>
   </si>
   <si>
-    <t>Communications</t>
-  </si>
-  <si>
     <t>22020</t>
   </si>
   <si>
@@ -712,18 +712,18 @@
     <t>Politique énergétique et gestion administrative</t>
   </si>
   <si>
+    <t>Politique de l'énergie</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>Energie</t>
+  </si>
+  <si>
     <t>231</t>
   </si>
   <si>
-    <t>Energie</t>
-  </si>
-  <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>Politique de l'énergie</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -748,12 +748,12 @@
     <t>Production d'énergie, sources renouvelables - multiples technologies</t>
   </si>
   <si>
+    <t>Production d'électricité, sources renouvelables</t>
+  </si>
+  <si>
     <t>232</t>
   </si>
   <si>
-    <t>Production d'électricité, sources renouvelables</t>
-  </si>
-  <si>
     <t>23220</t>
   </si>
   <si>
@@ -808,12 +808,12 @@
     <t>Production d'énergie, sources non renouvelables - non spécifié</t>
   </si>
   <si>
+    <t>Production d'électricité, sources non renouvelables</t>
+  </si>
+  <si>
     <t>233</t>
   </si>
   <si>
-    <t>Production d'électricité, sources non renouvelables</t>
-  </si>
-  <si>
     <t>23320</t>
   </si>
   <si>
@@ -859,24 +859,24 @@
     <t>Centrales nucléaires et sûreté nucléaire</t>
   </si>
   <si>
+    <t>Centrales nucléaires</t>
+  </si>
+  <si>
     <t>235</t>
   </si>
   <si>
-    <t>Centrales nucléaires</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
     <t>Production de chaleur seule</t>
   </si>
   <si>
+    <t>Distribution de l'énergie</t>
+  </si>
+  <si>
     <t>236</t>
   </si>
   <si>
-    <t>Distribution de l'énergie</t>
-  </si>
-  <si>
     <t>23620</t>
   </si>
   <si>
@@ -919,12 +919,12 @@
     <t>Politique des finances et gestion administrative</t>
   </si>
   <si>
+    <t>Banques et Services Financiers</t>
+  </si>
+  <si>
     <t>240</t>
   </si>
   <si>
-    <t>Banques et Services Financiers</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -961,12 +961,12 @@
     <t>Politique commerciale et administration</t>
   </si>
   <si>
+    <t>Entreprises et Autres Services</t>
+  </si>
+  <si>
     <t>250</t>
   </si>
   <si>
-    <t>Entreprises et Autres Services</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -991,18 +991,18 @@
     <t>Politique agricole et gestion administrative</t>
   </si>
   <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>Agriculture, Sylviculture, Pêche</t>
+  </si>
+  <si>
     <t>311</t>
   </si>
   <si>
-    <t>Agriculture, Sylviculture, Pêche</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1111,12 +1111,12 @@
     <t>Politique de la sylviculture et gestion administrative</t>
   </si>
   <si>
+    <t>Sylviculture</t>
+  </si>
+  <si>
     <t>312</t>
   </si>
   <si>
-    <t>Sylviculture</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1153,12 +1153,12 @@
     <t>Politique de la pêche et gestion administrative</t>
   </si>
   <si>
+    <t>Pêche</t>
+  </si>
+  <si>
     <t>313</t>
   </si>
   <si>
-    <t>Pêche</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1189,18 +1189,18 @@
     <t>Politique de l'industrie et gestion administrative</t>
   </si>
   <si>
+    <t>Industries Manufacturières</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>Industries Manufacturières, Extractives, Construct</t>
+  </si>
+  <si>
     <t>321</t>
   </si>
   <si>
-    <t>Industries Manufacturières, Extractives, Construct</t>
-  </si>
-  <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>Industries Manufacturières</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1315,12 +1315,12 @@
     <t>Politique de l'industrie extractive et gestion administrative</t>
   </si>
   <si>
+    <t>Industries Extractives</t>
+  </si>
+  <si>
     <t>322</t>
   </si>
   <si>
-    <t>Industries Extractives</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1381,24 +1381,24 @@
     <t>Politique de la construction et gestion administrative</t>
   </si>
   <si>
+    <t>Construction</t>
+  </si>
+  <si>
     <t>323</t>
   </si>
   <si>
-    <t>Construction</t>
-  </si>
-  <si>
     <t>33110</t>
   </si>
   <si>
     <t>Politique commerciale et gestion administrative</t>
   </si>
   <si>
+    <t>Politique Commerciale et Réglementations</t>
+  </si>
+  <si>
     <t>331</t>
   </si>
   <si>
-    <t>Politique Commerciale et Réglementations</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1435,24 +1435,24 @@
     <t>Politique du tourisme et gestion administrative</t>
   </si>
   <si>
+    <t>Tourisme</t>
+  </si>
+  <si>
     <t>332</t>
   </si>
   <si>
-    <t>Tourisme</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
     <t>Politique de l'environnement et gestion administrative</t>
   </si>
   <si>
+    <t>Protection de l'Environnement Général</t>
+  </si>
+  <si>
     <t>410</t>
   </si>
   <si>
-    <t>Protection de l'Environnement Général</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -1489,12 +1489,12 @@
     <t>Aide plurisectorielle</t>
   </si>
   <si>
+    <t>Autres Multisecteurs</t>
+  </si>
+  <si>
     <t>430</t>
   </si>
   <si>
-    <t>Autres Multisecteurs</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1555,36 +1555,36 @@
     <t>Aide relative au soutien budgétaire général</t>
   </si>
   <si>
+    <t>Soutien Budgétaire</t>
+  </si>
+  <si>
     <t>510</t>
   </si>
   <si>
-    <t>Soutien Budgétaire</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
     <t>Assistance alimentaire</t>
   </si>
   <si>
+    <t>Aide Alimentaire Dévelopmentale</t>
+  </si>
+  <si>
     <t>520</t>
   </si>
   <si>
-    <t>Aide Alimentaire Dévelopmentale</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
     <t>Subventions à l'importation (biens d'équipement)</t>
   </si>
   <si>
+    <t>Aide sous forme de Produits, Autre</t>
+  </si>
+  <si>
     <t>530</t>
   </si>
   <si>
-    <t>Aide sous forme de Produits, Autre</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -1597,12 +1597,12 @@
     <t>Actions se rapportant à la dette</t>
   </si>
   <si>
+    <t>Actions se Rapportant a la Dette</t>
+  </si>
+  <si>
     <t>600</t>
   </si>
   <si>
-    <t>Actions se Rapportant a la Dette</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -1645,12 +1645,12 @@
     <t>Assistance matérielle et services d'urgence</t>
   </si>
   <si>
+    <t>Intervention d'Urgence</t>
+  </si>
+  <si>
     <t>720</t>
   </si>
   <si>
-    <t>Intervention d'Urgence</t>
-  </si>
-  <si>
     <t>72040</t>
   </si>
   <si>
@@ -1669,58 +1669,58 @@
     <t>Reconstruction et réhabilitation immédiate post-urgence</t>
   </si>
   <si>
+    <t>Reconstruction &amp; Réhabilitation</t>
+  </si>
+  <si>
     <t>730</t>
   </si>
   <si>
-    <t>Reconstruction &amp; Réhabilitation</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
     <t>Préparation aux interventions multi-risques</t>
   </si>
   <si>
+    <t>Prévention catastrophes/Préparation à leur survenue</t>
+  </si>
+  <si>
     <t>740</t>
   </si>
   <si>
-    <t>Prévention catastrophes/Préparation à leur survenue</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Frais administratifs (non alloués par secteur)</t>
   </si>
   <si>
+    <t>Frais Administratifs des Donneurs</t>
+  </si>
+  <si>
     <t>910</t>
   </si>
   <si>
-    <t>Frais Administratifs des Donneurs</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
     <t>Refugiés/demandeurs d'asile dans les pays donneurs (non alloués)</t>
   </si>
   <si>
+    <t>Refugiés dans les Pays Donneurs</t>
+  </si>
+  <si>
     <t>930</t>
   </si>
   <si>
-    <t>Refugiés dans les Pays Donneurs</t>
-  </si>
-  <si>
     <t>99810</t>
   </si>
   <si>
     <t>Secteur non spécifié</t>
   </si>
   <si>
+    <t>Non Affecté / Non Specifié</t>
+  </si>
+  <si>
     <t>998</t>
-  </si>
-  <si>
-    <t>Non Affecté / Non Specifié</t>
   </si>
   <si>
     <t>99820</t>
@@ -4694,7 +4694,7 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E115" t="s">
         <v>233</v>
@@ -4703,7 +4703,7 @@
         <v>234</v>
       </c>
       <c r="G115" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="116" spans="1:7">

--- a/api/1/clv2/xlsx/fr/SectorGroup.xlsx
+++ b/api/1/clv2/xlsx/fr/SectorGroup.xlsx
@@ -28,15 +28,15 @@
     <t>codeforiati:category-name</t>
   </si>
   <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -49,15 +49,15 @@
     <t>Education, Niveau non spécifié</t>
   </si>
   <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
-    <t>Education</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -169,15 +169,15 @@
     <t>Santé, Général</t>
   </si>
   <si>
+    <t>Santé</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
-    <t>Santé</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -415,15 +415,15 @@
     <t>Gouvernement &amp; Société Civile-général</t>
   </si>
   <si>
+    <t>Gouvernement &amp; Société Civile</t>
+  </si>
+  <si>
+    <t>151</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
-    <t>Gouvernement &amp; Société Civile</t>
-  </si>
-  <si>
-    <t>151</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -715,15 +715,15 @@
     <t>Politique de l'énergie</t>
   </si>
   <si>
+    <t>Energie</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
-    <t>Energie</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -994,15 +994,15 @@
     <t>Agriculture</t>
   </si>
   <si>
+    <t>Agriculture, Sylviculture, Pêche</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
-    <t>Agriculture, Sylviculture, Pêche</t>
-  </si>
-  <si>
-    <t>311</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1192,13 +1192,13 @@
     <t>Industries Manufacturières</t>
   </si>
   <si>
+    <t>Industries Manufacturières, Extractives, Construct</t>
+  </si>
+  <si>
+    <t>321</t>
+  </si>
+  <si>
     <t>320</t>
-  </si>
-  <si>
-    <t>Industries Manufacturières, Extractives, Construct</t>
-  </si>
-  <si>
-    <t>321</t>
   </si>
   <si>
     <t>32120</t>
@@ -2193,10 +2193,10 @@
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2216,10 +2216,10 @@
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G7" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2239,10 +2239,10 @@
         <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2262,10 +2262,10 @@
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2285,10 +2285,10 @@
         <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G10" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2308,10 +2308,10 @@
         <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G11" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2331,10 +2331,10 @@
         <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G12" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2354,10 +2354,10 @@
         <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2377,10 +2377,10 @@
         <v>11</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="G14" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2400,10 +2400,10 @@
         <v>11</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="G15" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2423,10 +2423,10 @@
         <v>11</v>
       </c>
       <c r="F16" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="G16" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2538,10 +2538,10 @@
         <v>51</v>
       </c>
       <c r="F21" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G21" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2561,10 +2561,10 @@
         <v>51</v>
       </c>
       <c r="F22" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G22" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2584,10 +2584,10 @@
         <v>51</v>
       </c>
       <c r="F23" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G23" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2607,10 +2607,10 @@
         <v>51</v>
       </c>
       <c r="F24" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G24" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2630,10 +2630,10 @@
         <v>51</v>
       </c>
       <c r="F25" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G25" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2653,10 +2653,10 @@
         <v>51</v>
       </c>
       <c r="F26" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G26" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2676,10 +2676,10 @@
         <v>51</v>
       </c>
       <c r="F27" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G27" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2699,10 +2699,10 @@
         <v>51</v>
       </c>
       <c r="F28" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G28" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2722,10 +2722,10 @@
         <v>51</v>
       </c>
       <c r="F29" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G29" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2745,10 +2745,10 @@
         <v>51</v>
       </c>
       <c r="F30" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="G30" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2768,10 +2768,10 @@
         <v>51</v>
       </c>
       <c r="F31" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="G31" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2791,10 +2791,10 @@
         <v>51</v>
       </c>
       <c r="F32" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="G32" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2814,10 +2814,10 @@
         <v>51</v>
       </c>
       <c r="F33" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="G33" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2837,10 +2837,10 @@
         <v>51</v>
       </c>
       <c r="F34" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="G34" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2860,10 +2860,10 @@
         <v>51</v>
       </c>
       <c r="F35" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="G35" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2880,10 +2880,10 @@
         <v>96</v>
       </c>
       <c r="E36" t="s">
+        <v>96</v>
+      </c>
+      <c r="F36" t="s">
         <v>97</v>
-      </c>
-      <c r="F36" t="s">
-        <v>96</v>
       </c>
       <c r="G36" t="s">
         <v>97</v>
@@ -2903,10 +2903,10 @@
         <v>96</v>
       </c>
       <c r="E37" t="s">
+        <v>96</v>
+      </c>
+      <c r="F37" t="s">
         <v>97</v>
-      </c>
-      <c r="F37" t="s">
-        <v>96</v>
       </c>
       <c r="G37" t="s">
         <v>97</v>
@@ -2926,10 +2926,10 @@
         <v>96</v>
       </c>
       <c r="E38" t="s">
+        <v>96</v>
+      </c>
+      <c r="F38" t="s">
         <v>97</v>
-      </c>
-      <c r="F38" t="s">
-        <v>96</v>
       </c>
       <c r="G38" t="s">
         <v>97</v>
@@ -2949,10 +2949,10 @@
         <v>96</v>
       </c>
       <c r="E39" t="s">
+        <v>96</v>
+      </c>
+      <c r="F39" t="s">
         <v>97</v>
-      </c>
-      <c r="F39" t="s">
-        <v>96</v>
       </c>
       <c r="G39" t="s">
         <v>97</v>
@@ -2972,10 +2972,10 @@
         <v>96</v>
       </c>
       <c r="E40" t="s">
+        <v>96</v>
+      </c>
+      <c r="F40" t="s">
         <v>97</v>
-      </c>
-      <c r="F40" t="s">
-        <v>96</v>
       </c>
       <c r="G40" t="s">
         <v>97</v>
@@ -2995,10 +2995,10 @@
         <v>108</v>
       </c>
       <c r="E41" t="s">
+        <v>108</v>
+      </c>
+      <c r="F41" t="s">
         <v>109</v>
-      </c>
-      <c r="F41" t="s">
-        <v>108</v>
       </c>
       <c r="G41" t="s">
         <v>109</v>
@@ -3018,10 +3018,10 @@
         <v>108</v>
       </c>
       <c r="E42" t="s">
+        <v>108</v>
+      </c>
+      <c r="F42" t="s">
         <v>109</v>
-      </c>
-      <c r="F42" t="s">
-        <v>108</v>
       </c>
       <c r="G42" t="s">
         <v>109</v>
@@ -3041,10 +3041,10 @@
         <v>108</v>
       </c>
       <c r="E43" t="s">
+        <v>108</v>
+      </c>
+      <c r="F43" t="s">
         <v>109</v>
-      </c>
-      <c r="F43" t="s">
-        <v>108</v>
       </c>
       <c r="G43" t="s">
         <v>109</v>
@@ -3064,10 +3064,10 @@
         <v>108</v>
       </c>
       <c r="E44" t="s">
+        <v>108</v>
+      </c>
+      <c r="F44" t="s">
         <v>109</v>
-      </c>
-      <c r="F44" t="s">
-        <v>108</v>
       </c>
       <c r="G44" t="s">
         <v>109</v>
@@ -3087,10 +3087,10 @@
         <v>108</v>
       </c>
       <c r="E45" t="s">
+        <v>108</v>
+      </c>
+      <c r="F45" t="s">
         <v>109</v>
-      </c>
-      <c r="F45" t="s">
-        <v>108</v>
       </c>
       <c r="G45" t="s">
         <v>109</v>
@@ -3110,10 +3110,10 @@
         <v>108</v>
       </c>
       <c r="E46" t="s">
+        <v>108</v>
+      </c>
+      <c r="F46" t="s">
         <v>109</v>
-      </c>
-      <c r="F46" t="s">
-        <v>108</v>
       </c>
       <c r="G46" t="s">
         <v>109</v>
@@ -3133,10 +3133,10 @@
         <v>108</v>
       </c>
       <c r="E47" t="s">
+        <v>108</v>
+      </c>
+      <c r="F47" t="s">
         <v>109</v>
-      </c>
-      <c r="F47" t="s">
-        <v>108</v>
       </c>
       <c r="G47" t="s">
         <v>109</v>
@@ -3156,10 +3156,10 @@
         <v>108</v>
       </c>
       <c r="E48" t="s">
+        <v>108</v>
+      </c>
+      <c r="F48" t="s">
         <v>109</v>
-      </c>
-      <c r="F48" t="s">
-        <v>108</v>
       </c>
       <c r="G48" t="s">
         <v>109</v>
@@ -3179,10 +3179,10 @@
         <v>108</v>
       </c>
       <c r="E49" t="s">
+        <v>108</v>
+      </c>
+      <c r="F49" t="s">
         <v>109</v>
-      </c>
-      <c r="F49" t="s">
-        <v>108</v>
       </c>
       <c r="G49" t="s">
         <v>109</v>
@@ -3202,10 +3202,10 @@
         <v>108</v>
       </c>
       <c r="E50" t="s">
+        <v>108</v>
+      </c>
+      <c r="F50" t="s">
         <v>109</v>
-      </c>
-      <c r="F50" t="s">
-        <v>108</v>
       </c>
       <c r="G50" t="s">
         <v>109</v>
@@ -3225,10 +3225,10 @@
         <v>108</v>
       </c>
       <c r="E51" t="s">
+        <v>108</v>
+      </c>
+      <c r="F51" t="s">
         <v>109</v>
-      </c>
-      <c r="F51" t="s">
-        <v>108</v>
       </c>
       <c r="G51" t="s">
         <v>109</v>
@@ -3619,10 +3619,10 @@
         <v>133</v>
       </c>
       <c r="F68" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="G68" t="s">
-        <v>169</v>
+        <v>135</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3642,10 +3642,10 @@
         <v>133</v>
       </c>
       <c r="F69" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="G69" t="s">
-        <v>169</v>
+        <v>135</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3665,10 +3665,10 @@
         <v>133</v>
       </c>
       <c r="F70" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="G70" t="s">
-        <v>169</v>
+        <v>135</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3688,10 +3688,10 @@
         <v>133</v>
       </c>
       <c r="F71" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="G71" t="s">
-        <v>169</v>
+        <v>135</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3711,10 +3711,10 @@
         <v>133</v>
       </c>
       <c r="F72" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="G72" t="s">
-        <v>169</v>
+        <v>135</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3734,10 +3734,10 @@
         <v>133</v>
       </c>
       <c r="F73" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="G73" t="s">
-        <v>169</v>
+        <v>135</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3754,10 +3754,10 @@
         <v>182</v>
       </c>
       <c r="E74" t="s">
+        <v>182</v>
+      </c>
+      <c r="F74" t="s">
         <v>183</v>
-      </c>
-      <c r="F74" t="s">
-        <v>182</v>
       </c>
       <c r="G74" t="s">
         <v>183</v>
@@ -3777,10 +3777,10 @@
         <v>182</v>
       </c>
       <c r="E75" t="s">
+        <v>182</v>
+      </c>
+      <c r="F75" t="s">
         <v>183</v>
-      </c>
-      <c r="F75" t="s">
-        <v>182</v>
       </c>
       <c r="G75" t="s">
         <v>183</v>
@@ -3800,10 +3800,10 @@
         <v>182</v>
       </c>
       <c r="E76" t="s">
+        <v>182</v>
+      </c>
+      <c r="F76" t="s">
         <v>183</v>
-      </c>
-      <c r="F76" t="s">
-        <v>182</v>
       </c>
       <c r="G76" t="s">
         <v>183</v>
@@ -3823,10 +3823,10 @@
         <v>182</v>
       </c>
       <c r="E77" t="s">
+        <v>182</v>
+      </c>
+      <c r="F77" t="s">
         <v>183</v>
-      </c>
-      <c r="F77" t="s">
-        <v>182</v>
       </c>
       <c r="G77" t="s">
         <v>183</v>
@@ -3846,10 +3846,10 @@
         <v>182</v>
       </c>
       <c r="E78" t="s">
+        <v>182</v>
+      </c>
+      <c r="F78" t="s">
         <v>183</v>
-      </c>
-      <c r="F78" t="s">
-        <v>182</v>
       </c>
       <c r="G78" t="s">
         <v>183</v>
@@ -3869,10 +3869,10 @@
         <v>182</v>
       </c>
       <c r="E79" t="s">
+        <v>182</v>
+      </c>
+      <c r="F79" t="s">
         <v>183</v>
-      </c>
-      <c r="F79" t="s">
-        <v>182</v>
       </c>
       <c r="G79" t="s">
         <v>183</v>
@@ -3892,10 +3892,10 @@
         <v>182</v>
       </c>
       <c r="E80" t="s">
+        <v>182</v>
+      </c>
+      <c r="F80" t="s">
         <v>183</v>
-      </c>
-      <c r="F80" t="s">
-        <v>182</v>
       </c>
       <c r="G80" t="s">
         <v>183</v>
@@ -3915,10 +3915,10 @@
         <v>182</v>
       </c>
       <c r="E81" t="s">
+        <v>182</v>
+      </c>
+      <c r="F81" t="s">
         <v>183</v>
-      </c>
-      <c r="F81" t="s">
-        <v>182</v>
       </c>
       <c r="G81" t="s">
         <v>183</v>
@@ -3938,10 +3938,10 @@
         <v>182</v>
       </c>
       <c r="E82" t="s">
+        <v>182</v>
+      </c>
+      <c r="F82" t="s">
         <v>183</v>
-      </c>
-      <c r="F82" t="s">
-        <v>182</v>
       </c>
       <c r="G82" t="s">
         <v>183</v>
@@ -3961,10 +3961,10 @@
         <v>182</v>
       </c>
       <c r="E83" t="s">
+        <v>182</v>
+      </c>
+      <c r="F83" t="s">
         <v>183</v>
-      </c>
-      <c r="F83" t="s">
-        <v>182</v>
       </c>
       <c r="G83" t="s">
         <v>183</v>
@@ -3984,10 +3984,10 @@
         <v>182</v>
       </c>
       <c r="E84" t="s">
+        <v>182</v>
+      </c>
+      <c r="F84" t="s">
         <v>183</v>
-      </c>
-      <c r="F84" t="s">
-        <v>182</v>
       </c>
       <c r="G84" t="s">
         <v>183</v>
@@ -4007,10 +4007,10 @@
         <v>206</v>
       </c>
       <c r="E85" t="s">
+        <v>206</v>
+      </c>
+      <c r="F85" t="s">
         <v>207</v>
-      </c>
-      <c r="F85" t="s">
-        <v>206</v>
       </c>
       <c r="G85" t="s">
         <v>207</v>
@@ -4030,10 +4030,10 @@
         <v>206</v>
       </c>
       <c r="E86" t="s">
+        <v>206</v>
+      </c>
+      <c r="F86" t="s">
         <v>207</v>
-      </c>
-      <c r="F86" t="s">
-        <v>206</v>
       </c>
       <c r="G86" t="s">
         <v>207</v>
@@ -4053,10 +4053,10 @@
         <v>206</v>
       </c>
       <c r="E87" t="s">
+        <v>206</v>
+      </c>
+      <c r="F87" t="s">
         <v>207</v>
-      </c>
-      <c r="F87" t="s">
-        <v>206</v>
       </c>
       <c r="G87" t="s">
         <v>207</v>
@@ -4076,10 +4076,10 @@
         <v>206</v>
       </c>
       <c r="E88" t="s">
+        <v>206</v>
+      </c>
+      <c r="F88" t="s">
         <v>207</v>
-      </c>
-      <c r="F88" t="s">
-        <v>206</v>
       </c>
       <c r="G88" t="s">
         <v>207</v>
@@ -4099,10 +4099,10 @@
         <v>206</v>
       </c>
       <c r="E89" t="s">
+        <v>206</v>
+      </c>
+      <c r="F89" t="s">
         <v>207</v>
-      </c>
-      <c r="F89" t="s">
-        <v>206</v>
       </c>
       <c r="G89" t="s">
         <v>207</v>
@@ -4122,10 +4122,10 @@
         <v>206</v>
       </c>
       <c r="E90" t="s">
+        <v>206</v>
+      </c>
+      <c r="F90" t="s">
         <v>207</v>
-      </c>
-      <c r="F90" t="s">
-        <v>206</v>
       </c>
       <c r="G90" t="s">
         <v>207</v>
@@ -4145,10 +4145,10 @@
         <v>206</v>
       </c>
       <c r="E91" t="s">
+        <v>206</v>
+      </c>
+      <c r="F91" t="s">
         <v>207</v>
-      </c>
-      <c r="F91" t="s">
-        <v>206</v>
       </c>
       <c r="G91" t="s">
         <v>207</v>
@@ -4168,10 +4168,10 @@
         <v>222</v>
       </c>
       <c r="E92" t="s">
+        <v>222</v>
+      </c>
+      <c r="F92" t="s">
         <v>223</v>
-      </c>
-      <c r="F92" t="s">
-        <v>222</v>
       </c>
       <c r="G92" t="s">
         <v>223</v>
@@ -4191,10 +4191,10 @@
         <v>222</v>
       </c>
       <c r="E93" t="s">
+        <v>222</v>
+      </c>
+      <c r="F93" t="s">
         <v>223</v>
-      </c>
-      <c r="F93" t="s">
-        <v>222</v>
       </c>
       <c r="G93" t="s">
         <v>223</v>
@@ -4214,10 +4214,10 @@
         <v>222</v>
       </c>
       <c r="E94" t="s">
+        <v>222</v>
+      </c>
+      <c r="F94" t="s">
         <v>223</v>
-      </c>
-      <c r="F94" t="s">
-        <v>222</v>
       </c>
       <c r="G94" t="s">
         <v>223</v>
@@ -4237,10 +4237,10 @@
         <v>222</v>
       </c>
       <c r="E95" t="s">
+        <v>222</v>
+      </c>
+      <c r="F95" t="s">
         <v>223</v>
-      </c>
-      <c r="F95" t="s">
-        <v>222</v>
       </c>
       <c r="G95" t="s">
         <v>223</v>
@@ -4355,10 +4355,10 @@
         <v>233</v>
       </c>
       <c r="F100" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="G100" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4378,10 +4378,10 @@
         <v>233</v>
       </c>
       <c r="F101" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="G101" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4401,10 +4401,10 @@
         <v>233</v>
       </c>
       <c r="F102" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="G102" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4424,10 +4424,10 @@
         <v>233</v>
       </c>
       <c r="F103" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="G103" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4447,10 +4447,10 @@
         <v>233</v>
       </c>
       <c r="F104" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="G104" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4470,10 +4470,10 @@
         <v>233</v>
       </c>
       <c r="F105" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="G105" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4493,10 +4493,10 @@
         <v>233</v>
       </c>
       <c r="F106" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="G106" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4516,10 +4516,10 @@
         <v>233</v>
       </c>
       <c r="F107" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="G107" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4539,10 +4539,10 @@
         <v>233</v>
       </c>
       <c r="F108" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="G108" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4562,10 +4562,10 @@
         <v>233</v>
       </c>
       <c r="F109" t="s">
-        <v>234</v>
+        <v>265</v>
       </c>
       <c r="G109" t="s">
-        <v>265</v>
+        <v>235</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4585,10 +4585,10 @@
         <v>233</v>
       </c>
       <c r="F110" t="s">
-        <v>234</v>
+        <v>265</v>
       </c>
       <c r="G110" t="s">
-        <v>265</v>
+        <v>235</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4608,10 +4608,10 @@
         <v>233</v>
       </c>
       <c r="F111" t="s">
-        <v>234</v>
+        <v>265</v>
       </c>
       <c r="G111" t="s">
-        <v>265</v>
+        <v>235</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4631,10 +4631,10 @@
         <v>233</v>
       </c>
       <c r="F112" t="s">
-        <v>234</v>
+        <v>265</v>
       </c>
       <c r="G112" t="s">
-        <v>265</v>
+        <v>235</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4654,10 +4654,10 @@
         <v>233</v>
       </c>
       <c r="F113" t="s">
-        <v>234</v>
+        <v>265</v>
       </c>
       <c r="G113" t="s">
-        <v>265</v>
+        <v>235</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4677,10 +4677,10 @@
         <v>233</v>
       </c>
       <c r="F114" t="s">
-        <v>234</v>
+        <v>265</v>
       </c>
       <c r="G114" t="s">
-        <v>265</v>
+        <v>235</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4700,10 +4700,10 @@
         <v>233</v>
       </c>
       <c r="F115" t="s">
-        <v>234</v>
+        <v>278</v>
       </c>
       <c r="G115" t="s">
-        <v>278</v>
+        <v>235</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4723,10 +4723,10 @@
         <v>233</v>
       </c>
       <c r="F116" t="s">
-        <v>234</v>
+        <v>282</v>
       </c>
       <c r="G116" t="s">
-        <v>282</v>
+        <v>235</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4746,10 +4746,10 @@
         <v>233</v>
       </c>
       <c r="F117" t="s">
-        <v>234</v>
+        <v>286</v>
       </c>
       <c r="G117" t="s">
-        <v>286</v>
+        <v>235</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4769,10 +4769,10 @@
         <v>233</v>
       </c>
       <c r="F118" t="s">
-        <v>234</v>
+        <v>286</v>
       </c>
       <c r="G118" t="s">
-        <v>286</v>
+        <v>235</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4792,10 +4792,10 @@
         <v>233</v>
       </c>
       <c r="F119" t="s">
-        <v>234</v>
+        <v>286</v>
       </c>
       <c r="G119" t="s">
-        <v>286</v>
+        <v>235</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4815,10 +4815,10 @@
         <v>233</v>
       </c>
       <c r="F120" t="s">
-        <v>234</v>
+        <v>286</v>
       </c>
       <c r="G120" t="s">
-        <v>286</v>
+        <v>235</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4838,10 +4838,10 @@
         <v>233</v>
       </c>
       <c r="F121" t="s">
-        <v>234</v>
+        <v>286</v>
       </c>
       <c r="G121" t="s">
-        <v>286</v>
+        <v>235</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4861,10 +4861,10 @@
         <v>233</v>
       </c>
       <c r="F122" t="s">
-        <v>234</v>
+        <v>286</v>
       </c>
       <c r="G122" t="s">
-        <v>286</v>
+        <v>235</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4884,10 +4884,10 @@
         <v>233</v>
       </c>
       <c r="F123" t="s">
-        <v>234</v>
+        <v>286</v>
       </c>
       <c r="G123" t="s">
-        <v>286</v>
+        <v>235</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4904,10 +4904,10 @@
         <v>301</v>
       </c>
       <c r="E124" t="s">
+        <v>301</v>
+      </c>
+      <c r="F124" t="s">
         <v>302</v>
-      </c>
-      <c r="F124" t="s">
-        <v>301</v>
       </c>
       <c r="G124" t="s">
         <v>302</v>
@@ -4927,10 +4927,10 @@
         <v>301</v>
       </c>
       <c r="E125" t="s">
+        <v>301</v>
+      </c>
+      <c r="F125" t="s">
         <v>302</v>
-      </c>
-      <c r="F125" t="s">
-        <v>301</v>
       </c>
       <c r="G125" t="s">
         <v>302</v>
@@ -4950,10 +4950,10 @@
         <v>301</v>
       </c>
       <c r="E126" t="s">
+        <v>301</v>
+      </c>
+      <c r="F126" t="s">
         <v>302</v>
-      </c>
-      <c r="F126" t="s">
-        <v>301</v>
       </c>
       <c r="G126" t="s">
         <v>302</v>
@@ -4973,10 +4973,10 @@
         <v>301</v>
       </c>
       <c r="E127" t="s">
+        <v>301</v>
+      </c>
+      <c r="F127" t="s">
         <v>302</v>
-      </c>
-      <c r="F127" t="s">
-        <v>301</v>
       </c>
       <c r="G127" t="s">
         <v>302</v>
@@ -4996,10 +4996,10 @@
         <v>301</v>
       </c>
       <c r="E128" t="s">
+        <v>301</v>
+      </c>
+      <c r="F128" t="s">
         <v>302</v>
-      </c>
-      <c r="F128" t="s">
-        <v>301</v>
       </c>
       <c r="G128" t="s">
         <v>302</v>
@@ -5019,10 +5019,10 @@
         <v>301</v>
       </c>
       <c r="E129" t="s">
+        <v>301</v>
+      </c>
+      <c r="F129" t="s">
         <v>302</v>
-      </c>
-      <c r="F129" t="s">
-        <v>301</v>
       </c>
       <c r="G129" t="s">
         <v>302</v>
@@ -5042,10 +5042,10 @@
         <v>315</v>
       </c>
       <c r="E130" t="s">
+        <v>315</v>
+      </c>
+      <c r="F130" t="s">
         <v>316</v>
-      </c>
-      <c r="F130" t="s">
-        <v>315</v>
       </c>
       <c r="G130" t="s">
         <v>316</v>
@@ -5065,10 +5065,10 @@
         <v>315</v>
       </c>
       <c r="E131" t="s">
+        <v>315</v>
+      </c>
+      <c r="F131" t="s">
         <v>316</v>
-      </c>
-      <c r="F131" t="s">
-        <v>315</v>
       </c>
       <c r="G131" t="s">
         <v>316</v>
@@ -5088,10 +5088,10 @@
         <v>315</v>
       </c>
       <c r="E132" t="s">
+        <v>315</v>
+      </c>
+      <c r="F132" t="s">
         <v>316</v>
-      </c>
-      <c r="F132" t="s">
-        <v>315</v>
       </c>
       <c r="G132" t="s">
         <v>316</v>
@@ -5111,10 +5111,10 @@
         <v>315</v>
       </c>
       <c r="E133" t="s">
+        <v>315</v>
+      </c>
+      <c r="F133" t="s">
         <v>316</v>
-      </c>
-      <c r="F133" t="s">
-        <v>315</v>
       </c>
       <c r="G133" t="s">
         <v>316</v>
@@ -5551,10 +5551,10 @@
         <v>326</v>
       </c>
       <c r="F152" t="s">
-        <v>327</v>
+        <v>366</v>
       </c>
       <c r="G152" t="s">
-        <v>366</v>
+        <v>328</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5574,10 +5574,10 @@
         <v>326</v>
       </c>
       <c r="F153" t="s">
-        <v>327</v>
+        <v>366</v>
       </c>
       <c r="G153" t="s">
-        <v>366</v>
+        <v>328</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5597,10 +5597,10 @@
         <v>326</v>
       </c>
       <c r="F154" t="s">
-        <v>327</v>
+        <v>366</v>
       </c>
       <c r="G154" t="s">
-        <v>366</v>
+        <v>328</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5620,10 +5620,10 @@
         <v>326</v>
       </c>
       <c r="F155" t="s">
-        <v>327</v>
+        <v>366</v>
       </c>
       <c r="G155" t="s">
-        <v>366</v>
+        <v>328</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5643,10 +5643,10 @@
         <v>326</v>
       </c>
       <c r="F156" t="s">
-        <v>327</v>
+        <v>366</v>
       </c>
       <c r="G156" t="s">
-        <v>366</v>
+        <v>328</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5666,10 +5666,10 @@
         <v>326</v>
       </c>
       <c r="F157" t="s">
-        <v>327</v>
+        <v>366</v>
       </c>
       <c r="G157" t="s">
-        <v>366</v>
+        <v>328</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5689,10 +5689,10 @@
         <v>326</v>
       </c>
       <c r="F158" t="s">
-        <v>327</v>
+        <v>380</v>
       </c>
       <c r="G158" t="s">
-        <v>380</v>
+        <v>328</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -5712,10 +5712,10 @@
         <v>326</v>
       </c>
       <c r="F159" t="s">
-        <v>327</v>
+        <v>380</v>
       </c>
       <c r="G159" t="s">
-        <v>380</v>
+        <v>328</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -5735,10 +5735,10 @@
         <v>326</v>
       </c>
       <c r="F160" t="s">
-        <v>327</v>
+        <v>380</v>
       </c>
       <c r="G160" t="s">
-        <v>380</v>
+        <v>328</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -5758,10 +5758,10 @@
         <v>326</v>
       </c>
       <c r="F161" t="s">
-        <v>327</v>
+        <v>380</v>
       </c>
       <c r="G161" t="s">
-        <v>380</v>
+        <v>328</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -5781,10 +5781,10 @@
         <v>326</v>
       </c>
       <c r="F162" t="s">
-        <v>327</v>
+        <v>380</v>
       </c>
       <c r="G162" t="s">
-        <v>380</v>
+        <v>328</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -6241,10 +6241,10 @@
         <v>392</v>
       </c>
       <c r="F182" t="s">
-        <v>393</v>
+        <v>434</v>
       </c>
       <c r="G182" t="s">
-        <v>434</v>
+        <v>394</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6264,10 +6264,10 @@
         <v>392</v>
       </c>
       <c r="F183" t="s">
-        <v>393</v>
+        <v>434</v>
       </c>
       <c r="G183" t="s">
-        <v>434</v>
+        <v>394</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6287,10 +6287,10 @@
         <v>392</v>
       </c>
       <c r="F184" t="s">
-        <v>393</v>
+        <v>434</v>
       </c>
       <c r="G184" t="s">
-        <v>434</v>
+        <v>394</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6310,10 +6310,10 @@
         <v>392</v>
       </c>
       <c r="F185" t="s">
-        <v>393</v>
+        <v>434</v>
       </c>
       <c r="G185" t="s">
-        <v>434</v>
+        <v>394</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6333,10 +6333,10 @@
         <v>392</v>
       </c>
       <c r="F186" t="s">
-        <v>393</v>
+        <v>434</v>
       </c>
       <c r="G186" t="s">
-        <v>434</v>
+        <v>394</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6356,10 +6356,10 @@
         <v>392</v>
       </c>
       <c r="F187" t="s">
-        <v>393</v>
+        <v>434</v>
       </c>
       <c r="G187" t="s">
-        <v>434</v>
+        <v>394</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6379,10 +6379,10 @@
         <v>392</v>
       </c>
       <c r="F188" t="s">
-        <v>393</v>
+        <v>434</v>
       </c>
       <c r="G188" t="s">
-        <v>434</v>
+        <v>394</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -6402,10 +6402,10 @@
         <v>392</v>
       </c>
       <c r="F189" t="s">
-        <v>393</v>
+        <v>434</v>
       </c>
       <c r="G189" t="s">
-        <v>434</v>
+        <v>394</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6425,10 +6425,10 @@
         <v>392</v>
       </c>
       <c r="F190" t="s">
-        <v>393</v>
+        <v>434</v>
       </c>
       <c r="G190" t="s">
-        <v>434</v>
+        <v>394</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6448,10 +6448,10 @@
         <v>392</v>
       </c>
       <c r="F191" t="s">
-        <v>393</v>
+        <v>434</v>
       </c>
       <c r="G191" t="s">
-        <v>434</v>
+        <v>394</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6471,10 +6471,10 @@
         <v>392</v>
       </c>
       <c r="F192" t="s">
-        <v>393</v>
+        <v>456</v>
       </c>
       <c r="G192" t="s">
-        <v>456</v>
+        <v>394</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6491,10 +6491,10 @@
         <v>459</v>
       </c>
       <c r="E193" t="s">
+        <v>459</v>
+      </c>
+      <c r="F193" t="s">
         <v>460</v>
-      </c>
-      <c r="F193" t="s">
-        <v>459</v>
       </c>
       <c r="G193" t="s">
         <v>460</v>
@@ -6514,10 +6514,10 @@
         <v>459</v>
       </c>
       <c r="E194" t="s">
+        <v>459</v>
+      </c>
+      <c r="F194" t="s">
         <v>460</v>
-      </c>
-      <c r="F194" t="s">
-        <v>459</v>
       </c>
       <c r="G194" t="s">
         <v>460</v>
@@ -6537,10 +6537,10 @@
         <v>459</v>
       </c>
       <c r="E195" t="s">
+        <v>459</v>
+      </c>
+      <c r="F195" t="s">
         <v>460</v>
-      </c>
-      <c r="F195" t="s">
-        <v>459</v>
       </c>
       <c r="G195" t="s">
         <v>460</v>
@@ -6560,10 +6560,10 @@
         <v>459</v>
       </c>
       <c r="E196" t="s">
+        <v>459</v>
+      </c>
+      <c r="F196" t="s">
         <v>460</v>
-      </c>
-      <c r="F196" t="s">
-        <v>459</v>
       </c>
       <c r="G196" t="s">
         <v>460</v>
@@ -6583,10 +6583,10 @@
         <v>459</v>
       </c>
       <c r="E197" t="s">
+        <v>459</v>
+      </c>
+      <c r="F197" t="s">
         <v>460</v>
-      </c>
-      <c r="F197" t="s">
-        <v>459</v>
       </c>
       <c r="G197" t="s">
         <v>460</v>
@@ -6606,10 +6606,10 @@
         <v>459</v>
       </c>
       <c r="E198" t="s">
+        <v>459</v>
+      </c>
+      <c r="F198" t="s">
         <v>460</v>
-      </c>
-      <c r="F198" t="s">
-        <v>459</v>
       </c>
       <c r="G198" t="s">
         <v>460</v>
@@ -6629,10 +6629,10 @@
         <v>473</v>
       </c>
       <c r="E199" t="s">
+        <v>473</v>
+      </c>
+      <c r="F199" t="s">
         <v>474</v>
-      </c>
-      <c r="F199" t="s">
-        <v>473</v>
       </c>
       <c r="G199" t="s">
         <v>474</v>
@@ -6652,10 +6652,10 @@
         <v>477</v>
       </c>
       <c r="E200" t="s">
+        <v>477</v>
+      </c>
+      <c r="F200" t="s">
         <v>478</v>
-      </c>
-      <c r="F200" t="s">
-        <v>477</v>
       </c>
       <c r="G200" t="s">
         <v>478</v>
@@ -6675,10 +6675,10 @@
         <v>477</v>
       </c>
       <c r="E201" t="s">
+        <v>477</v>
+      </c>
+      <c r="F201" t="s">
         <v>478</v>
-      </c>
-      <c r="F201" t="s">
-        <v>477</v>
       </c>
       <c r="G201" t="s">
         <v>478</v>
@@ -6698,10 +6698,10 @@
         <v>477</v>
       </c>
       <c r="E202" t="s">
+        <v>477</v>
+      </c>
+      <c r="F202" t="s">
         <v>478</v>
-      </c>
-      <c r="F202" t="s">
-        <v>477</v>
       </c>
       <c r="G202" t="s">
         <v>478</v>
@@ -6721,10 +6721,10 @@
         <v>477</v>
       </c>
       <c r="E203" t="s">
+        <v>477</v>
+      </c>
+      <c r="F203" t="s">
         <v>478</v>
-      </c>
-      <c r="F203" t="s">
-        <v>477</v>
       </c>
       <c r="G203" t="s">
         <v>478</v>
@@ -6744,10 +6744,10 @@
         <v>477</v>
       </c>
       <c r="E204" t="s">
+        <v>477</v>
+      </c>
+      <c r="F204" t="s">
         <v>478</v>
-      </c>
-      <c r="F204" t="s">
-        <v>477</v>
       </c>
       <c r="G204" t="s">
         <v>478</v>
@@ -6767,10 +6767,10 @@
         <v>477</v>
       </c>
       <c r="E205" t="s">
+        <v>477</v>
+      </c>
+      <c r="F205" t="s">
         <v>478</v>
-      </c>
-      <c r="F205" t="s">
-        <v>477</v>
       </c>
       <c r="G205" t="s">
         <v>478</v>
@@ -6790,10 +6790,10 @@
         <v>491</v>
       </c>
       <c r="E206" t="s">
+        <v>491</v>
+      </c>
+      <c r="F206" t="s">
         <v>492</v>
-      </c>
-      <c r="F206" t="s">
-        <v>491</v>
       </c>
       <c r="G206" t="s">
         <v>492</v>
@@ -6813,10 +6813,10 @@
         <v>491</v>
       </c>
       <c r="E207" t="s">
+        <v>491</v>
+      </c>
+      <c r="F207" t="s">
         <v>492</v>
-      </c>
-      <c r="F207" t="s">
-        <v>491</v>
       </c>
       <c r="G207" t="s">
         <v>492</v>
@@ -6836,10 +6836,10 @@
         <v>491</v>
       </c>
       <c r="E208" t="s">
+        <v>491</v>
+      </c>
+      <c r="F208" t="s">
         <v>492</v>
-      </c>
-      <c r="F208" t="s">
-        <v>491</v>
       </c>
       <c r="G208" t="s">
         <v>492</v>
@@ -6859,10 +6859,10 @@
         <v>491</v>
       </c>
       <c r="E209" t="s">
+        <v>491</v>
+      </c>
+      <c r="F209" t="s">
         <v>492</v>
-      </c>
-      <c r="F209" t="s">
-        <v>491</v>
       </c>
       <c r="G209" t="s">
         <v>492</v>
@@ -6882,10 +6882,10 @@
         <v>491</v>
       </c>
       <c r="E210" t="s">
+        <v>491</v>
+      </c>
+      <c r="F210" t="s">
         <v>492</v>
-      </c>
-      <c r="F210" t="s">
-        <v>491</v>
       </c>
       <c r="G210" t="s">
         <v>492</v>
@@ -6905,10 +6905,10 @@
         <v>491</v>
       </c>
       <c r="E211" t="s">
+        <v>491</v>
+      </c>
+      <c r="F211" t="s">
         <v>492</v>
-      </c>
-      <c r="F211" t="s">
-        <v>491</v>
       </c>
       <c r="G211" t="s">
         <v>492</v>
@@ -6928,10 +6928,10 @@
         <v>491</v>
       </c>
       <c r="E212" t="s">
+        <v>491</v>
+      </c>
+      <c r="F212" t="s">
         <v>492</v>
-      </c>
-      <c r="F212" t="s">
-        <v>491</v>
       </c>
       <c r="G212" t="s">
         <v>492</v>
@@ -6951,10 +6951,10 @@
         <v>491</v>
       </c>
       <c r="E213" t="s">
+        <v>491</v>
+      </c>
+      <c r="F213" t="s">
         <v>492</v>
-      </c>
-      <c r="F213" t="s">
-        <v>491</v>
       </c>
       <c r="G213" t="s">
         <v>492</v>
@@ -6974,10 +6974,10 @@
         <v>491</v>
       </c>
       <c r="E214" t="s">
+        <v>491</v>
+      </c>
+      <c r="F214" t="s">
         <v>492</v>
-      </c>
-      <c r="F214" t="s">
-        <v>491</v>
       </c>
       <c r="G214" t="s">
         <v>492</v>
@@ -6997,10 +6997,10 @@
         <v>491</v>
       </c>
       <c r="E215" t="s">
+        <v>491</v>
+      </c>
+      <c r="F215" t="s">
         <v>492</v>
-      </c>
-      <c r="F215" t="s">
-        <v>491</v>
       </c>
       <c r="G215" t="s">
         <v>492</v>
@@ -7020,10 +7020,10 @@
         <v>513</v>
       </c>
       <c r="E216" t="s">
+        <v>513</v>
+      </c>
+      <c r="F216" t="s">
         <v>514</v>
-      </c>
-      <c r="F216" t="s">
-        <v>513</v>
       </c>
       <c r="G216" t="s">
         <v>514</v>
@@ -7043,10 +7043,10 @@
         <v>517</v>
       </c>
       <c r="E217" t="s">
+        <v>517</v>
+      </c>
+      <c r="F217" t="s">
         <v>518</v>
-      </c>
-      <c r="F217" t="s">
-        <v>517</v>
       </c>
       <c r="G217" t="s">
         <v>518</v>
@@ -7066,10 +7066,10 @@
         <v>521</v>
       </c>
       <c r="E218" t="s">
+        <v>521</v>
+      </c>
+      <c r="F218" t="s">
         <v>522</v>
-      </c>
-      <c r="F218" t="s">
-        <v>521</v>
       </c>
       <c r="G218" t="s">
         <v>522</v>
@@ -7089,10 +7089,10 @@
         <v>521</v>
       </c>
       <c r="E219" t="s">
+        <v>521</v>
+      </c>
+      <c r="F219" t="s">
         <v>522</v>
-      </c>
-      <c r="F219" t="s">
-        <v>521</v>
       </c>
       <c r="G219" t="s">
         <v>522</v>
@@ -7112,10 +7112,10 @@
         <v>527</v>
       </c>
       <c r="E220" t="s">
+        <v>527</v>
+      </c>
+      <c r="F220" t="s">
         <v>528</v>
-      </c>
-      <c r="F220" t="s">
-        <v>527</v>
       </c>
       <c r="G220" t="s">
         <v>528</v>
@@ -7135,10 +7135,10 @@
         <v>527</v>
       </c>
       <c r="E221" t="s">
+        <v>527</v>
+      </c>
+      <c r="F221" t="s">
         <v>528</v>
-      </c>
-      <c r="F221" t="s">
-        <v>527</v>
       </c>
       <c r="G221" t="s">
         <v>528</v>
@@ -7158,10 +7158,10 @@
         <v>527</v>
       </c>
       <c r="E222" t="s">
+        <v>527</v>
+      </c>
+      <c r="F222" t="s">
         <v>528</v>
-      </c>
-      <c r="F222" t="s">
-        <v>527</v>
       </c>
       <c r="G222" t="s">
         <v>528</v>
@@ -7181,10 +7181,10 @@
         <v>527</v>
       </c>
       <c r="E223" t="s">
+        <v>527</v>
+      </c>
+      <c r="F223" t="s">
         <v>528</v>
-      </c>
-      <c r="F223" t="s">
-        <v>527</v>
       </c>
       <c r="G223" t="s">
         <v>528</v>
@@ -7204,10 +7204,10 @@
         <v>527</v>
       </c>
       <c r="E224" t="s">
+        <v>527</v>
+      </c>
+      <c r="F224" t="s">
         <v>528</v>
-      </c>
-      <c r="F224" t="s">
-        <v>527</v>
       </c>
       <c r="G224" t="s">
         <v>528</v>
@@ -7227,10 +7227,10 @@
         <v>527</v>
       </c>
       <c r="E225" t="s">
+        <v>527</v>
+      </c>
+      <c r="F225" t="s">
         <v>528</v>
-      </c>
-      <c r="F225" t="s">
-        <v>527</v>
       </c>
       <c r="G225" t="s">
         <v>528</v>
@@ -7250,10 +7250,10 @@
         <v>527</v>
       </c>
       <c r="E226" t="s">
+        <v>527</v>
+      </c>
+      <c r="F226" t="s">
         <v>528</v>
-      </c>
-      <c r="F226" t="s">
-        <v>527</v>
       </c>
       <c r="G226" t="s">
         <v>528</v>
@@ -7273,10 +7273,10 @@
         <v>543</v>
       </c>
       <c r="E227" t="s">
+        <v>543</v>
+      </c>
+      <c r="F227" t="s">
         <v>544</v>
-      </c>
-      <c r="F227" t="s">
-        <v>543</v>
       </c>
       <c r="G227" t="s">
         <v>544</v>
@@ -7296,10 +7296,10 @@
         <v>543</v>
       </c>
       <c r="E228" t="s">
+        <v>543</v>
+      </c>
+      <c r="F228" t="s">
         <v>544</v>
-      </c>
-      <c r="F228" t="s">
-        <v>543</v>
       </c>
       <c r="G228" t="s">
         <v>544</v>
@@ -7319,10 +7319,10 @@
         <v>543</v>
       </c>
       <c r="E229" t="s">
+        <v>543</v>
+      </c>
+      <c r="F229" t="s">
         <v>544</v>
-      </c>
-      <c r="F229" t="s">
-        <v>543</v>
       </c>
       <c r="G229" t="s">
         <v>544</v>
@@ -7342,10 +7342,10 @@
         <v>551</v>
       </c>
       <c r="E230" t="s">
+        <v>551</v>
+      </c>
+      <c r="F230" t="s">
         <v>552</v>
-      </c>
-      <c r="F230" t="s">
-        <v>551</v>
       </c>
       <c r="G230" t="s">
         <v>552</v>
@@ -7365,10 +7365,10 @@
         <v>555</v>
       </c>
       <c r="E231" t="s">
+        <v>555</v>
+      </c>
+      <c r="F231" t="s">
         <v>556</v>
-      </c>
-      <c r="F231" t="s">
-        <v>555</v>
       </c>
       <c r="G231" t="s">
         <v>556</v>
@@ -7388,10 +7388,10 @@
         <v>559</v>
       </c>
       <c r="E232" t="s">
+        <v>559</v>
+      </c>
+      <c r="F232" t="s">
         <v>560</v>
-      </c>
-      <c r="F232" t="s">
-        <v>559</v>
       </c>
       <c r="G232" t="s">
         <v>560</v>
@@ -7411,10 +7411,10 @@
         <v>563</v>
       </c>
       <c r="E233" t="s">
+        <v>563</v>
+      </c>
+      <c r="F233" t="s">
         <v>564</v>
-      </c>
-      <c r="F233" t="s">
-        <v>563</v>
       </c>
       <c r="G233" t="s">
         <v>564</v>
@@ -7434,10 +7434,10 @@
         <v>567</v>
       </c>
       <c r="E234" t="s">
+        <v>567</v>
+      </c>
+      <c r="F234" t="s">
         <v>568</v>
-      </c>
-      <c r="F234" t="s">
-        <v>567</v>
       </c>
       <c r="G234" t="s">
         <v>568</v>
@@ -7457,10 +7457,10 @@
         <v>567</v>
       </c>
       <c r="E235" t="s">
+        <v>567</v>
+      </c>
+      <c r="F235" t="s">
         <v>568</v>
-      </c>
-      <c r="F235" t="s">
-        <v>567</v>
       </c>
       <c r="G235" t="s">
         <v>568</v>
